--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -2436,8 +2436,15 @@
         <v>45522.64583333334</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>14650</v>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>GnizyMB7</t>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27906</v>
+        <v>43147</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,199 +574,953 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">doveri d 
+          <t xml:space="preserve">rapuano a 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>77</v>
+      </c>
+      <c r="K3" t="n">
+        <v>771</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>77</v>
+      </c>
+      <c r="K4" t="n">
+        <v>771</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>77</v>
+      </c>
+      <c r="K5" t="n">
+        <v>771</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45530.5625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>771</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45530.65625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">giua a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>77</v>
+      </c>
+      <c r="K7" t="n">
+        <v>771</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45534.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>77</v>
+      </c>
+      <c r="K8" t="n">
+        <v>771</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>771</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>771</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>771</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>771</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>771</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>771</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" t="n">
+        <v>771</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>77</v>
+      </c>
+      <c r="K16" t="n">
+        <v>771</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">bluenergy stadium   stadio friuli
   udine </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E17" t="n">
         <v>25144</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>rXw8YKDE</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>udinese</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>lazio</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>77</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K17" t="n">
         <v>771</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M17" t="n">
         <v>20242025</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>AsIP75lK</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45528.65625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di marco d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>inter</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>lecce</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>77</v>
-      </c>
-      <c r="K4" t="n">
-        <v>771</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>6D3e2qCs</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45528.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mariani m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>17102</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>genoa</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>77</v>
-      </c>
-      <c r="K5" t="n">
-        <v>771</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45530.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">di bello m 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>43147</v>
+        <v>16416</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>como</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45530.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">giua a 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28177</v>
+        <v>39211</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
-        </is>
-      </c>
+        <v>45534.5625</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70634</v>
+        <v>11150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +703,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
+        <v>45534.65625</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54726</v>
+        <v>80018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +765,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45530.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
+        <v>45535.5625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16416</v>
+        <v>38279</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,45 +827,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45530.65625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">giua a 
-  ita </t>
-        </is>
-      </c>
+        <v>45535.5625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39211</v>
+        <v>40670</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -909,40 +889,40 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11150</v>
+        <v>70634</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -971,40 +951,40 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80018</v>
+        <v>54726</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1033,40 +1013,40 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>38279</v>
+        <v>43147</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1095,40 +1075,40 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40670</v>
+        <v>36599</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1157,40 +1137,40 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70634</v>
+        <v>41507</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1219,40 +1199,40 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>54726</v>
+        <v>25144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>como</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1273,254 +1253,6 @@
         </is>
       </c>
       <c r="O13" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>77</v>
-      </c>
-      <c r="K14" t="n">
-        <v>771</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>genoa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>77</v>
-      </c>
-      <c r="K15" t="n">
-        <v>771</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>77</v>
-      </c>
-      <c r="K16" t="n">
-        <v>771</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>77</v>
-      </c>
-      <c r="K17" t="n">
-        <v>771</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,40 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45530.5625</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
+        <v>45534.5625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16416</v>
+        <v>11150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +569,40 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45530.65625</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">giua a 
-  ita </t>
-        </is>
-      </c>
+        <v>45534.65625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39211</v>
+        <v>80018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,40 +631,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11150</v>
+        <v>38279</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -703,40 +693,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80018</v>
+        <v>40670</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -765,40 +755,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38279</v>
+        <v>70634</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -827,40 +817,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40670</v>
+        <v>54726</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -889,40 +879,40 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70634</v>
+        <v>43147</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -951,40 +941,40 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>54726</v>
+        <v>36599</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1013,40 +1003,40 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>43147</v>
+        <v>41507</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1075,40 +1065,40 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>36599</v>
+        <v>25144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>como</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1129,130 +1119,6 @@
         </is>
       </c>
       <c r="O11" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>77</v>
-      </c>
-      <c r="K12" t="n">
-        <v>771</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>77</v>
-      </c>
-      <c r="K13" t="n">
-        <v>771</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,40 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.5625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45535.5625</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11150</v>
+        <v>38279</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -569,40 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45534.65625</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45535.5625</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>80018</v>
+        <v>40670</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -631,40 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.5625</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45535.65625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38279</v>
+        <v>70634</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -693,40 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.5625</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45535.65625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40670</v>
+        <v>54726</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -755,40 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.65625</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45536.5625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70634</v>
+        <v>43147</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,40 +842,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.65625</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45536.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54726</v>
+        <v>36599</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -879,40 +909,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45536.65625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>43147</v>
+        <v>41507</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -941,40 +976,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45536.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36599</v>
+        <v>25144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>como</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -995,130 +1035,6 @@
         </is>
       </c>
       <c r="O9" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>77</v>
-      </c>
-      <c r="K10" t="n">
-        <v>771</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>77</v>
-      </c>
-      <c r="K11" t="n">
-        <v>771</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">marinelli l 
+          <t xml:space="preserve">colombo a 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38279</v>
+        <v>43147</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fabbri m 
+          <t xml:space="preserve">ayroldi g 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40670</v>
+        <v>36599</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">massa d 
+          <t xml:space="preserve">guida m 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70634</v>
+        <v>41507</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tremolada p 
+          <t xml:space="preserve">prontera a 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54726</v>
+        <v>25144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>como</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -767,274 +767,6 @@
         </is>
       </c>
       <c r="O5" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>77</v>
-      </c>
-      <c r="K6" t="n">
-        <v>771</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>genoa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>77</v>
-      </c>
-      <c r="K7" t="n">
-        <v>771</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>77</v>
-      </c>
-      <c r="K8" t="n">
-        <v>771</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>77</v>
-      </c>
-      <c r="K9" t="n">
-        <v>771</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,40 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>n7VN5MCd</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>43147</v>
+        <v>13602</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>como</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +569,40 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>v1I9TP43</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
+        <v>45549.54166666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36599</v>
+        <v>16284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +631,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
-        </is>
-      </c>
+        <v>45549.65625</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>41507</v>
+        <v>80018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +693,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
+        <v>45550.3125</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25144</v>
+        <v>36599</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -767,6 +747,378 @@
         </is>
       </c>
       <c r="O5" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>21747</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>771</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>77</v>
+      </c>
+      <c r="K7" t="n">
+        <v>771</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.54166666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>77</v>
+      </c>
+      <c r="K8" t="n">
+        <v>771</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>771</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45551.5625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>771</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45551.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>771</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,626 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45555.5625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>771</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>771</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.41666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>771</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.54166666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" t="n">
+        <v>771</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.65625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>77</v>
+      </c>
+      <c r="K16" t="n">
+        <v>771</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.3125</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>77</v>
+      </c>
+      <c r="K17" t="n">
+        <v>771</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>77</v>
+      </c>
+      <c r="K18" t="n">
+        <v>771</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>77</v>
+      </c>
+      <c r="K19" t="n">
+        <v>771</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>77</v>
+      </c>
+      <c r="K20" t="n">
+        <v>771</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45558.65625</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>21747</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>77</v>
+      </c>
+      <c r="K21" t="n">
+        <v>771</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,467 +507,1238 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>2ucWYubt</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.3125</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">giua a 
-  ita </t>
-        </is>
-      </c>
+        <v>45555.5625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K2" t="n">
+        <v>771</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>77</v>
+      </c>
+      <c r="K3" t="n">
+        <v>771</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.41666666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>77</v>
+      </c>
+      <c r="K4" t="n">
+        <v>771</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>77</v>
+      </c>
+      <c r="K5" t="n">
+        <v>771</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.65625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>771</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45557.3125</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>77</v>
+      </c>
+      <c r="K7" t="n">
+        <v>771</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>77</v>
+      </c>
+      <c r="K8" t="n">
+        <v>771</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>771</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>771</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45558.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>771</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45562.65625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>771</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>771</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.54166666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio luigi ferraris
   genoa </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E14" t="n">
         <v>36599</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>d0PJxeie</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>genoa</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>77</v>
-      </c>
-      <c r="K2" t="n">
-        <v>771</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sacchi j  l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>21747</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>771</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>atalanta</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>77</v>
-      </c>
-      <c r="K3" t="n">
-        <v>771</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>4WHcOkpL</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="J15" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" t="n">
+        <v>771</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45564.3125</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio olimpico di torino
   turin </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E16" t="n">
         <v>28177</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>MZFZnvX4</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>torino</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>lecce</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>77</v>
-      </c>
-      <c r="K4" t="n">
-        <v>771</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>16416</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cagliari</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>77</v>
+      </c>
+      <c r="K16" t="n">
+        <v>771</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>77</v>
+      </c>
+      <c r="K17" t="n">
+        <v>771</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>77</v>
+      </c>
+      <c r="K18" t="n">
+        <v>771</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.54166666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>77</v>
+      </c>
+      <c r="K19" t="n">
+        <v>771</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>napoli</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>77</v>
-      </c>
-      <c r="K5" t="n">
-        <v>771</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>17102</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>monza</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>inter</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>77</v>
-      </c>
-      <c r="K6" t="n">
-        <v>771</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45551.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">abisso r 
-  ita </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="J20" t="n">
+        <v>77</v>
+      </c>
+      <c r="K20" t="n">
+        <v>771</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45565.65625</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio ennio tardini
   parma </t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E21" t="n">
         <v>27906</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>6DxlaxHN</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>parma</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>77</v>
-      </c>
-      <c r="K7" t="n">
-        <v>771</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45551.65625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>lazio</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>77</v>
-      </c>
-      <c r="K8" t="n">
-        <v>771</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>77</v>
+      </c>
+      <c r="K21" t="n">
+        <v>771</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,40 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2ucWYubt</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45555.5625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45556.41666666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16416</v>
+        <v>11150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -569,40 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>44gmVcc5</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45555.65625</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45556.54166666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39211</v>
+        <v>41507</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -631,40 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>S66wtFBN</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45556.65625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11150</v>
+        <v>40670</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -693,40 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Yqo4RFdU</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45557.3125</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41507</v>
+        <v>43147</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -755,40 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>O8QDoJsn</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45556.65625</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40670</v>
+        <v>17102</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,40 +842,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>A50vXJSh</t>
+          <t>WvDUsysB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45557.3125</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43147</v>
+        <v>70634</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -879,40 +909,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pOEMqcCb</t>
+          <t>xIieTySH</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45557.41666666666</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45557.65625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17102</v>
+        <v>80018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -941,40 +976,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WvDUsysB</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45557.54166666666</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45558.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70634</v>
+        <v>24950</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>como</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -995,750 +1035,6 @@
         </is>
       </c>
       <c r="O9" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xIieTySH</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45557.65625</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>inter</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ac milan</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>77</v>
-      </c>
-      <c r="K10" t="n">
-        <v>771</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45558.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>24950</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>atalanta</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>77</v>
-      </c>
-      <c r="K11" t="n">
-        <v>771</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45562.65625</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ac milan</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>lecce</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>77</v>
-      </c>
-      <c r="K12" t="n">
-        <v>771</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45563.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>inter</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>77</v>
-      </c>
-      <c r="K13" t="n">
-        <v>771</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45563.54166666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>genoa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>77</v>
-      </c>
-      <c r="K14" t="n">
-        <v>771</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45563.65625</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>38279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>bologna</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>atalanta</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>77</v>
-      </c>
-      <c r="K15" t="n">
-        <v>771</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45564.3125</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>28177</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>torino</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>lazio</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>77</v>
-      </c>
-      <c r="K16" t="n">
-        <v>771</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>venezia</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>77</v>
-      </c>
-      <c r="K17" t="n">
-        <v>771</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giuseppe sinigaglia
-  como </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>13602</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>77</v>
-      </c>
-      <c r="K18" t="n">
-        <v>771</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45564.54166666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio carlo castellani
-  empoli </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>16284</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>empoli</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>77</v>
-      </c>
-      <c r="K19" t="n">
-        <v>771</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>napoli</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>77</v>
-      </c>
-      <c r="K20" t="n">
-        <v>771</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45565.65625</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>27906</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>parma</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>cagliari</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>77</v>
-      </c>
-      <c r="K21" t="n">
-        <v>771</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,467 +507,1305 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.3125</v>
+        <v>45558.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">giua a 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K2" t="n">
+        <v>771</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45562.65625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>77</v>
+      </c>
+      <c r="K3" t="n">
+        <v>771</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>77</v>
+      </c>
+      <c r="K4" t="n">
+        <v>771</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio luigi ferraris
   genoa </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E5" t="n">
         <v>36599</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>d0PJxeie</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>genoa</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>77</v>
+      </c>
+      <c r="K5" t="n">
+        <v>771</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.65625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>771</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45564.3125</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>77</v>
+      </c>
+      <c r="K7" t="n">
+        <v>771</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>zVqqL0ma</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>as roma</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>77</v>
-      </c>
-      <c r="K2" t="n">
-        <v>771</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sacchi j  l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>77</v>
+      </c>
+      <c r="K8" t="n">
+        <v>771</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>771</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.54166666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>771</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>771</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45565.65625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>771</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45569.5625</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>771</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45569.65625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>771</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" t="n">
+        <v>771</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.54166666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">gewiss stadium
   bergamo </t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>21747</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E16" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>atalanta</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>77</v>
-      </c>
-      <c r="K3" t="n">
-        <v>771</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>4WHcOkpL</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio olimpico di torino
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>77</v>
+      </c>
+      <c r="K16" t="n">
+        <v>771</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45570.65625</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>77</v>
+      </c>
+      <c r="K17" t="n">
+        <v>771</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.3125</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
   turin </t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>28177</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>torino</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>lecce</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>77</v>
-      </c>
-      <c r="K4" t="n">
-        <v>771</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>16416</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E18" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>SCGVmKHb</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>cagliari</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>napoli</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>77</v>
-      </c>
-      <c r="K5" t="n">
-        <v>771</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="J18" t="n">
+        <v>77</v>
+      </c>
+      <c r="K18" t="n">
+        <v>771</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>77</v>
+      </c>
+      <c r="K19" t="n">
+        <v>771</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>77</v>
+      </c>
+      <c r="K20" t="n">
+        <v>771</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45571.54166666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">brianteo
   monza </t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E21" t="n">
         <v>17102</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>monza</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>inter</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>77</v>
-      </c>
-      <c r="K6" t="n">
-        <v>771</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45551.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">abisso r 
-  ita </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>27906</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>parma</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>77</v>
-      </c>
-      <c r="K7" t="n">
-        <v>771</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45551.65625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>lazio</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>77</v>
-      </c>
-      <c r="K8" t="n">
-        <v>771</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>77</v>
+      </c>
+      <c r="K21" t="n">
+        <v>771</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>77</v>
+      </c>
+      <c r="K22" t="n">
+        <v>771</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45558.65625</v>
+        <v>45562.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tremolada p 
+          <t xml:space="preserve">zufferli l 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24950</v>
+        <v>80018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,40 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45562.65625</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>80018</v>
+        <v>25144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -636,40 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45563.54166666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25144</v>
+        <v>36599</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -698,40 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45563.65625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36599</v>
+        <v>38279</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -760,40 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45563.65625</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45564.3125</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38279</v>
+        <v>28177</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -822,40 +842,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45564.3125</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28177</v>
+        <v>70634</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -884,40 +909,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>45564.41666666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">giua a 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70634</v>
+        <v>13602</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>como</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -946,40 +976,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45564.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe sinigaglia
-  como </t>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13602</v>
+        <v>16284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1008,40 +1043,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45564.54166666666</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45564.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio carlo castellani
-  empoli </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>16284</v>
+        <v>54726</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1062,750 +1102,6 @@
         </is>
       </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>napoli</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>77</v>
-      </c>
-      <c r="K11" t="n">
-        <v>771</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45565.65625</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>27906</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>parma</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>cagliari</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>77</v>
-      </c>
-      <c r="K12" t="n">
-        <v>771</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45569.5625</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>napoli</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>77</v>
-      </c>
-      <c r="K13" t="n">
-        <v>771</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8SWavWAa</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45569.65625</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>39211</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>venezia</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>77</v>
-      </c>
-      <c r="K14" t="n">
-        <v>771</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45570.41666666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>lecce</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>77</v>
-      </c>
-      <c r="K15" t="n">
-        <v>771</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>EB8yv2aJ</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45570.54166666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>24950</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>atalanta</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>genoa</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>77</v>
-      </c>
-      <c r="K16" t="n">
-        <v>771</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ttV7xAuC</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45570.65625</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>inter</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>torino</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>77</v>
-      </c>
-      <c r="K17" t="n">
-        <v>771</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>x8OGzlAO</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.3125</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>cagliari</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>77</v>
-      </c>
-      <c r="K18" t="n">
-        <v>771</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dzYLoEIP</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>38279</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>bologna</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>parma</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>77</v>
-      </c>
-      <c r="K19" t="n">
-        <v>771</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SW3Qfiet</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>lazio</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>empoli</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>77</v>
-      </c>
-      <c r="K20" t="n">
-        <v>771</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>lnhZhVPh</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45571.54166666666</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>17102</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>77</v>
-      </c>
-      <c r="K21" t="n">
-        <v>771</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SIOithtm</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>ac milan</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>77</v>
-      </c>
-      <c r="K22" t="n">
-        <v>771</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.65625</v>
+        <v>45564.3125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zufferli l 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80018</v>
+        <v>28177</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.41666666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25144</v>
+        <v>70634</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.54166666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
+          <t xml:space="preserve">giua a 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36599</v>
+        <v>13602</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>como</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.65625</v>
+        <v>45564.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">aureliano g 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38279</v>
+        <v>16284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45564.3125</v>
+        <v>45564.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28177</v>
+        <v>54726</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,45 +842,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45565.65625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">abisso r 
+          <t xml:space="preserve">fourneau f 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70634</v>
+        <v>27906</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -901,207 +901,6 @@
         </is>
       </c>
       <c r="O7" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">giua a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giuseppe sinigaglia
-  como </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>13602</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>77</v>
-      </c>
-      <c r="K8" t="n">
-        <v>771</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.54166666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aureliano g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio carlo castellani
-  empoli </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>16284</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>empoli</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>77</v>
-      </c>
-      <c r="K9" t="n">
-        <v>771</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">manganiello g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>napoli</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>77</v>
-      </c>
-      <c r="K10" t="n">
-        <v>771</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.3125</v>
+        <v>45569.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">feliciani e 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28177</v>
+        <v>54726</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>como</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,35 +574,35 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45569.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">abisso r 
+          <t xml:space="preserve">guida m 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70634</v>
+        <v>39211</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>WUqjkmPH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45570.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">giua a 
+          <t xml:space="preserve">mariani m 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe sinigaglia
-  como </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>13602</v>
+        <v>25144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.54166666666</v>
+        <v>45570.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">aureliano g 
+          <t xml:space="preserve">chiffi d 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio carlo castellani
-  empoli </t>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16284</v>
+        <v>24950</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45564.65625</v>
+        <v>45570.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54726</v>
+        <v>80018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,35 +842,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45565.65625</v>
+        <v>45571.3125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fourneau f 
+          <t xml:space="preserve">marinelli l 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27906</v>
+        <v>41507</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -901,6 +901,398 @@
         </is>
       </c>
       <c r="O7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>77</v>
+      </c>
+      <c r="K8" t="n">
+        <v>771</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>771</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.54166666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>771</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>771</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>771</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>771</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.5625</v>
+        <v>45571.3125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">feliciani e 
+          <t xml:space="preserve">marinelli l 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54726</v>
+        <v>41507</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">guida m 
+          <t xml:space="preserve">di bello m 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39211</v>
+        <v>38279</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.41666666666</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
+          <t xml:space="preserve">ayroldi g 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25144</v>
+        <v>70634</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.54166666666</v>
+        <v>45571.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">chiffi d 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24950</v>
+        <v>17102</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.65625</v>
+        <v>45571.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">marcenaro m 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>80018</v>
+        <v>43147</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,45 +842,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.3125</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marinelli l 
-  ita </t>
-        </is>
-      </c>
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41507</v>
+        <v>13602</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>como</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -909,45 +904,40 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>38279</v>
+        <v>36599</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>0M9xNN8N</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>bologna</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>parma</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -976,45 +966,40 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
+        <v>45584.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70634</v>
+        <v>80018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1043,45 +1028,40 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.54166666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
+        <v>45584.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17102</v>
+        <v>41507</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1110,45 +1090,40 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
+        <v>45585.3125</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>43147</v>
+        <v>16284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1177,40 +1152,40 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe sinigaglia
-  como </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13602</v>
+        <v>40670</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1239,40 +1214,40 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36599</v>
+        <v>11150</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1293,6 +1268,130 @@
         </is>
       </c>
       <c r="O13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45585.54166666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>771</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" t="n">
+        <v>771</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,12 @@
       <c r="B2" s="2" t="n">
         <v>45584.41666666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio giuseppe sinigaglia
@@ -575,7 +580,12 @@
       <c r="B3" s="2" t="n">
         <v>45584.41666666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio luigi ferraris
@@ -637,7 +647,12 @@
       <c r="B4" s="2" t="n">
         <v>45584.54166666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio giuseppe meazza  san siro 
@@ -699,7 +714,12 @@
       <c r="B5" s="2" t="n">
         <v>45584.65625</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">allianz stadium
@@ -761,7 +781,12 @@
       <c r="B6" s="2" t="n">
         <v>45585.3125</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio carlo castellani
@@ -823,7 +848,12 @@
       <c r="B7" s="2" t="n">
         <v>45585.41666666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio via del mare
@@ -885,7 +915,12 @@
       <c r="B8" s="2" t="n">
         <v>45585.41666666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio pierluigi penzo
@@ -947,7 +982,12 @@
       <c r="B9" s="2" t="n">
         <v>45585.54166666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">unipol domus
@@ -1009,7 +1049,12 @@
       <c r="B10" s="2" t="n">
         <v>45585.65625</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio olimpico
@@ -1071,7 +1116,12 @@
       <c r="B11" s="2" t="n">
         <v>45586.65625</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio marc antonio bentegodi
@@ -1925,6 +1975,316 @@
         </is>
       </c>
       <c r="O24" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>77</v>
+      </c>
+      <c r="K25" t="n">
+        <v>771</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>77</v>
+      </c>
+      <c r="K26" t="n">
+        <v>771</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>77</v>
+      </c>
+      <c r="K27" t="n">
+        <v>771</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>77</v>
+      </c>
+      <c r="K28" t="n">
+        <v>771</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45596.60416666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>77</v>
+      </c>
+      <c r="K29" t="n">
+        <v>771</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2290,6 +2290,130 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>77</v>
+      </c>
+      <c r="K30" t="n">
+        <v>771</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>77</v>
+      </c>
+      <c r="K31" t="n">
+        <v>771</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,400 +507,1858 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.3125</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">abisso r 
-  ita </t>
-        </is>
-      </c>
+        <v>45590.5625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K2" t="n">
+        <v>771</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>bLD0NyVN</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45590.65625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>77</v>
+      </c>
+      <c r="K3" t="n">
+        <v>771</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>UuMqRJVb</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.41666666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>77</v>
+      </c>
+      <c r="K4" t="n">
+        <v>771</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>8f71RSPs</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>77</v>
+      </c>
+      <c r="K5" t="n">
+        <v>771</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.65625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>771</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.35416666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>77</v>
+      </c>
+      <c r="K7" t="n">
+        <v>771</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>77</v>
+      </c>
+      <c r="K8" t="n">
+        <v>771</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>771</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>771</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>771</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45594.60416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>771</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45594.60416666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>771</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45594.69791666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>771</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio carlo castellani
   empoli </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E15" t="n">
         <v>16284</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>0ESCnI1H</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>empoli</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>napoli</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>77</v>
-      </c>
-      <c r="K2" t="n">
-        <v>771</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>AJ5eIkmR</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45585.41666666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fourneau f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>40670</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>lecce</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>77</v>
-      </c>
-      <c r="K3" t="n">
-        <v>771</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>dGwq9oAD</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45585.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" t="n">
+        <v>771</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio pierluigi penzo
   venice </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E16" t="n">
         <v>11150</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>MkPmVv50</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>venezia</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>77</v>
+      </c>
+      <c r="K16" t="n">
+        <v>771</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>atalanta</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>77</v>
-      </c>
-      <c r="K4" t="n">
-        <v>771</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>GMBD7YY8</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45585.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aureliano g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>16416</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cagliari</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>torino</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>77</v>
-      </c>
-      <c r="K5" t="n">
-        <v>771</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>0lpzB7u1</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45585.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">massa d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>77</v>
+      </c>
+      <c r="K17" t="n">
+        <v>771</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>77</v>
+      </c>
+      <c r="K18" t="n">
+        <v>771</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45596.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>77</v>
+      </c>
+      <c r="K19" t="n">
+        <v>771</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio olimpico
   rome </t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E20" t="n">
         <v>70634</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>zVqqL0ma</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>as roma</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>inter</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>77</v>
-      </c>
-      <c r="K6" t="n">
-        <v>771</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>McP0d8Q7</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45586.65625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dionisi f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>77</v>
+      </c>
+      <c r="K20" t="n">
+        <v>771</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>77</v>
+      </c>
+      <c r="K21" t="n">
+        <v>771</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45598.45833333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>77</v>
+      </c>
+      <c r="K22" t="n">
+        <v>771</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45598.58333333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>77</v>
+      </c>
+      <c r="K23" t="n">
+        <v>771</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45598.69791666666</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>77</v>
+      </c>
+      <c r="K24" t="n">
+        <v>771</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45599.35416666666</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>77</v>
+      </c>
+      <c r="K25" t="n">
+        <v>771</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>77</v>
+      </c>
+      <c r="K26" t="n">
+        <v>771</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45599.58333333334</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio marc antonio bentegodi
   verona </t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E27" t="n">
         <v>39211</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>rJVAIaHo</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>verona</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>77</v>
-      </c>
-      <c r="K7" t="n">
-        <v>771</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>77</v>
+      </c>
+      <c r="K27" t="n">
+        <v>771</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>77</v>
+      </c>
+      <c r="K28" t="n">
+        <v>771</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>77</v>
+      </c>
+      <c r="K29" t="n">
+        <v>771</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>77</v>
+      </c>
+      <c r="K30" t="n">
+        <v>771</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45600.69791666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>77</v>
+      </c>
+      <c r="K31" t="n">
+        <v>771</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,601 +507,1908 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.5625</v>
+        <v>45594.60416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">fourneau f 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K2" t="n">
+        <v>771</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45594.60416666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>77</v>
+      </c>
+      <c r="K3" t="n">
+        <v>771</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45594.69791666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>77</v>
+      </c>
+      <c r="K4" t="n">
+        <v>771</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>77</v>
+      </c>
+      <c r="K5" t="n">
+        <v>771</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>771</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>77</v>
+      </c>
+      <c r="K7" t="n">
+        <v>771</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>77</v>
+      </c>
+      <c r="K8" t="n">
+        <v>771</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45596.60416666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>771</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>771</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>771</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45598.45833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>771</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">bluenergy stadium   stadio friuli
   udine </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E13" t="n">
         <v>25144</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>rXw8YKDE</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>udinese</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>cagliari</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>77</v>
-      </c>
-      <c r="K2" t="n">
-        <v>771</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>bLD0NyVN</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45590.65625</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>771</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.69791666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>771</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45599.35416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" t="n">
+        <v>771</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio olimpico di torino
   turin </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E16" t="n">
         <v>28177</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>MZFZnvX4</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>torino</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>77</v>
+      </c>
+      <c r="K16" t="n">
+        <v>771</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.58333333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>77</v>
+      </c>
+      <c r="K17" t="n">
+        <v>771</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>77</v>
+      </c>
+      <c r="K18" t="n">
+        <v>771</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>ttyLthOA</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>como</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>77</v>
-      </c>
-      <c r="K3" t="n">
-        <v>771</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>UuMqRJVb</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45591.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>napoli</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="J19" t="n">
+        <v>77</v>
+      </c>
+      <c r="K19" t="n">
+        <v>771</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>77</v>
+      </c>
+      <c r="K20" t="n">
+        <v>771</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45600.69791666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>77</v>
+      </c>
+      <c r="K21" t="n">
+        <v>771</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>bR8Aj2ug</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45603.69791666666</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>77</v>
+      </c>
+      <c r="K22" t="n">
+        <v>771</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>G8lYsMgU</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>lecce</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>77</v>
-      </c>
-      <c r="K4" t="n">
-        <v>771</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>OMVUWl2K</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45591.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feliciani e 
-  ita </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>77</v>
+      </c>
+      <c r="K23" t="n">
+        <v>771</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45605.45833333334</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>77</v>
+      </c>
+      <c r="K24" t="n">
+        <v>771</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>E3zhYKPO</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45605.58333333334</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>77</v>
+      </c>
+      <c r="K25" t="n">
+        <v>771</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>S60RnKvI</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45605.69791666666</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>77</v>
+      </c>
+      <c r="K26" t="n">
+        <v>771</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>tjxpzseC</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45606.35416666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">gewiss stadium
   bergamo </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E27" t="n">
         <v>24950</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>atalanta</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>77</v>
-      </c>
-      <c r="K5" t="n">
-        <v>771</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>jeAhPc0B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45592.35416666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>27906</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>parma</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>empoli</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>77</v>
-      </c>
-      <c r="K6" t="n">
-        <v>771</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>OjcQLOgJ</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45592.45833333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">piccinini m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>77</v>
+      </c>
+      <c r="K27" t="n">
+        <v>771</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>pbap3uPb</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio olimpico
   rome </t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E28" t="n">
         <v>70634</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>lazio</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>genoa</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>77</v>
-      </c>
-      <c r="K7" t="n">
-        <v>771</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>xY3xTu1n</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45592.45833333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rapuano a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>77</v>
+      </c>
+      <c r="K28" t="n">
+        <v>771</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>hU52hOAt</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>77</v>
+      </c>
+      <c r="K29" t="n">
+        <v>771</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45606.58333333334</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t xml:space="preserve">brianteo
   monza </t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E30" t="n">
         <v>17102</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>monza</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>venezia</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>77</v>
-      </c>
-      <c r="K8" t="n">
-        <v>771</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>jwaINpP6</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45592.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>77</v>
+      </c>
+      <c r="K30" t="n">
+        <v>771</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>KtcJltA5</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45606.69791666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio giuseppe meazza  san siro 
   milan </t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E31" t="n">
         <v>80018</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Iw7eKK25</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>inter</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>77</v>
-      </c>
-      <c r="K9" t="n">
-        <v>771</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>fB59P6ff</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45592.69791666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sozza s 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>77</v>
-      </c>
-      <c r="K10" t="n">
-        <v>771</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>77</v>
+      </c>
+      <c r="K31" t="n">
+        <v>771</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -507,40 +507,40 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45598.45833333334</v>
+        <v>45603.69791666666</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38279</v>
+        <v>36599</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>como</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -569,40 +569,40 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.58333333334</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25144</v>
+        <v>40670</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -631,40 +631,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.69791666666</v>
+        <v>45605.45833333334</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17102</v>
+        <v>11150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -693,40 +693,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45599.35416666666</v>
+        <v>45605.58333333334</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54726</v>
+        <v>16416</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -755,40 +755,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45605.69791666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
+          <t xml:space="preserve">allianz stadium
   turin </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28177</v>
+        <v>41507</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>MZFZnvX4</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>torino</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,40 +817,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.58333333334</v>
+        <v>45606.35416666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39211</v>
+        <v>24950</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -879,40 +879,40 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>80018</v>
+        <v>70634</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -941,40 +941,40 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45600.60416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio carlo castellani
-  empoli </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16284</v>
+        <v>43147</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1003,40 +1003,40 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45600.60416666666</v>
+        <v>45606.58333333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>27906</v>
+        <v>17102</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1065,40 +1065,40 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45600.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70634</v>
+        <v>80018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="J11" t="n">

--- a/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/italy/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,40 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45603.69791666666</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36599</v>
+        <v>40670</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -569,40 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45604.69791666666</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45605.45833333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40670</v>
+        <v>11150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -631,40 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45605.45833333334</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45605.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11150</v>
+        <v>16416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -693,40 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45605.58333333334</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45605.69791666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16416</v>
+        <v>41507</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -755,40 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45605.69791666666</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45606.35416666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>41507</v>
+        <v>24950</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,40 +842,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45606.35416666666</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24950</v>
+        <v>70634</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -879,40 +909,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>45606.45833333334</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70634</v>
+        <v>43147</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -941,40 +976,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45606.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>43147</v>
+        <v>17102</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1003,40 +1043,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45606.58333333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45606.69791666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17102</v>
+        <v>80018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1065,60 +1110,122 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45606.69791666666</v>
+        <v>45619.45833333334</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>771</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z7KrCz8T</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.58333333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
           <t xml:space="preserve">stadio giuseppe meazza  san siro 
   milan </t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>80018</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>inter</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>napoli</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>77</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>771</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>20242025</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
